--- a/data/sars/alaska/tables/Alaska_2006_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2006_Appendix2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795AC60A-FEE3-B142-AA0C-88FBA423B3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761BF8F4-F0FB-E648-9515-A55113C250A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{1A3A7482-8109-5C4D-96D6-34CBF7676409}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="75">
   <si>
     <t>Alaska</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>comments</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -387,7 +393,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -565,6 +571,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -728,7 +740,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -736,7 +748,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1114,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB57880-618F-B248-848C-122DCA7CEB04}">
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -1122,7 +1140,7 @@
     <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
@@ -1166,10 +1184,13 @@
         <v>71</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -1204,42 +1225,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
         <v>0.12</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="3">
         <v>0.5</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
+      <c r="J3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3">
         <v>0.68</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="4">
         <v>6788</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="4">
         <v>6789</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O3" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1283,7 +1307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1327,7 +1351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1371,7 +1395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1415,95 +1439,101 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="3">
         <v>278</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="3">
         <v>0.18</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="3">
         <v>238</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>6</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="3">
         <v>2005</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="3">
         <v>0.04</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="3">
         <v>0.3</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="O8" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>10545</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="3">
         <v>0.13</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="4">
         <v>9472</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="3">
         <v>2001</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="3">
         <v>0.04</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="3">
         <v>0.5</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="3">
         <v>95</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="3">
         <v>0.2</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="3">
         <v>39</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="3">
         <v>40</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1538,95 +1568,101 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4">
         <v>83400</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="3">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="E11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
         <v>5</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="3">
         <v>2000</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="3">
         <v>0.04</v>
       </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="3">
         <v>30</v>
       </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
         <v>30</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N11" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="O11" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="3">
         <v>5703</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
         <v>5703</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>2</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="3">
         <v>2003</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="3">
         <v>0.04</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="3">
         <v>0.1</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="3">
         <v>11.4</v>
       </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>0.2</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="N12" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1670,453 +1706,483 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="4">
         <v>17076</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="3">
         <v>0.26500000000000001</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="4">
         <v>13713</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>8</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="3">
         <v>1997</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="3">
         <v>0.04</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="3">
         <v>0.5</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="3">
         <v>137</v>
       </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1" t="s">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="O14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="4">
         <v>41854</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="3">
         <v>0.224</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="4">
         <v>34740</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>7</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="3">
         <v>1998</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="3">
         <v>0.04</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="3">
         <v>0.5</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="3">
         <v>347</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15" s="3">
         <v>68</v>
       </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>70</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="N15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="O15" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>66078</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="3">
         <v>0.23200000000000001</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="4">
         <v>54492</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>6</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="3">
         <v>1999</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="3">
         <v>0.04</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="3">
         <v>0.5</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="3">
         <v>545</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16" s="3">
         <v>0.35</v>
       </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
         <v>0.35</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N16" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="O16" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="4">
         <v>112391</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="3">
         <v>0.04</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="4">
         <v>108670</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>6</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="3">
         <v>0.12</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="3">
         <v>0.5</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="4">
         <v>3260</v>
       </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2">
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
         <v>1092</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="4">
         <v>1094</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="N17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="O17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P17" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="4">
         <v>45975</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="3">
         <v>0.04</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="4">
         <v>44453</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>6</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="3">
         <v>2000</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="3">
         <v>0.12</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="3">
         <v>0.5</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="4">
         <v>1334</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="3">
         <v>24</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="3">
         <v>795</v>
       </c>
-      <c r="M18" s="1">
+      <c r="M18" s="3">
         <v>820</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="N18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="O18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P18" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="4">
         <v>21651</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="3">
         <v>0.1</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="4">
         <v>20109</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>6</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="3">
         <v>0.12</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="3">
         <v>0.5</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="3">
         <v>603</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="3">
         <v>1.3</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="3">
         <v>174</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M19" s="3">
         <v>177</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="N19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="O19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P19" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="3">
         <v>394</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="3">
         <v>0.08</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="3">
         <v>367</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="3">
         <v>1999</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="3">
         <v>0.1</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="3">
         <v>1.3</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="3">
         <v>0.2</v>
       </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>0.2</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="N20" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="O20" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="4">
         <v>4005</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="3">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="4">
         <v>3698</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>12</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="3">
         <v>1993</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="3">
         <v>0.1</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="3">
         <v>12.9</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="3">
         <v>3.2</v>
       </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>5</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N21" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="O21" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="3">
         <v>961</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="3">
         <v>0.12</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="3">
         <v>868</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="3">
         <v>0.1</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="3">
         <v>3</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="3">
         <v>1.4</v>
       </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>2.8</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="N22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="4">
         <v>1123</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="D23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4">
         <v>1123</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="3">
         <v>2003</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="3">
         <v>0.04</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="3">
         <v>0.5</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="3">
         <v>11.2</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="3">
         <v>1.5</v>
       </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>1.5</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N23" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -2154,7 +2220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,51 +2258,54 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="3">
         <v>314</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="D26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
         <v>314</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="3">
         <v>2003</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="3">
         <v>0.04</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="3">
         <v>0.5</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="3">
         <v>3.1</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26" s="3">
         <v>0.4</v>
       </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>0.4</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="N26" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -2274,314 +2343,338 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="B28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3">
         <v>0.04</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="3">
         <v>0.5</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
+      <c r="J28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3">
         <v>0.32</v>
       </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
         <v>0.32</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="N28" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+      <c r="O28" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="C29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3">
         <v>0.04</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="3">
         <v>0.1</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1" t="s">
+      <c r="J29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+      <c r="O29" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="4">
         <v>721935</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="D30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4">
         <v>709881</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="4">
         <v>2</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="3">
         <v>2004</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="3">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="3">
         <v>0.5</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="4">
         <v>15262</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K30" s="3">
         <v>0.5</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="3">
         <v>754</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M30" s="3">
         <v>756</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="O30" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="4">
         <v>26880</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1" t="s">
+      <c r="D31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="3">
         <v>1990</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="3">
         <v>0.04</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31" s="3">
         <v>0.5</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1" t="s">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+      <c r="O31" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1">
+      <c r="B32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3">
         <v>0.12</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32" s="3">
         <v>0.5</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="J32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3">
         <v>0.8</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32" s="3">
         <v>193</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M32" s="3">
         <v>194</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="N32" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="O32" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1">
+      <c r="B33" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3">
         <v>0.12</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="3">
         <v>0.5</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
+      <c r="J33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K33" s="3">
         <v>0.71</v>
       </c>
-      <c r="L33" s="2">
+      <c r="L33" s="4">
         <v>9567</v>
       </c>
-      <c r="M33" s="2">
+      <c r="M33" s="4">
         <v>9568</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="N33" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+      <c r="O33" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1">
+      <c r="C34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3">
         <v>0.04</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="3">
         <v>0.1</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
+      <c r="J34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K34" s="3">
         <v>0.5</v>
       </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
         <v>0.5</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="N34" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+      <c r="O34" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="1">
+      <c r="B35" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
         <v>0.12</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="3">
         <v>0.5</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
+      <c r="J35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K35" s="3">
         <v>0.88</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35" s="4">
         <v>5265</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35" s="4">
         <v>5266</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="N35" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
@@ -2616,86 +2709,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="4">
         <v>47885</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="4">
         <v>44555</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="4">
         <v>2</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="3">
         <v>2005</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="3">
         <v>0.12</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="3">
         <v>0.75</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="4">
         <v>2000</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K37" s="3">
         <v>2.6</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L37" s="3">
         <v>6</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M37" s="3">
         <v>10.199999999999999</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="N37" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+      <c r="O37" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="4">
         <v>38988</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="4">
         <v>38988</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="4">
         <v>2</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="3">
         <v>2004</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="3">
         <v>0.12</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="3">
         <v>0.1</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="3">
         <v>234</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38" s="3">
         <v>24.6</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L38" s="3">
         <v>191</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="3">
         <v>216</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="N38" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
